--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.25734853029394</v>
+      </c>
+      <c r="C2">
         <v>26.23155368926215</v>
-      </c>
-      <c r="C2">
-        <v>29.25734853029394</v>
       </c>
       <c r="D2">
         <v>3.812202707647274</v>
       </c>
       <c r="E2">
-        <v>16.87037037037037</v>
+        <v>18.81635802469136</v>
       </c>
       <c r="F2">
         <v>64.31327160493828</v>
       </c>
       <c r="G2">
-        <v>18.81635802469136</v>
+        <v>16.87037037037037</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>22.35294117647059</v>
+      </c>
+      <c r="C3">
         <v>40.78431372549019</v>
-      </c>
-      <c r="C3">
-        <v>22.35294117647059</v>
       </c>
       <c r="D3">
         <v>2.451923076923077</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>13.70192307692308</v>
       </c>
       <c r="F3">
         <v>61.29807692307693</v>
       </c>
       <c r="G3">
-        <v>13.70192307692308</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.5347745387051</v>
+      </c>
+      <c r="C4">
         <v>25.50496779124359</v>
-      </c>
-      <c r="C4">
-        <v>28.5347745387051</v>
       </c>
       <c r="D4">
         <v>3.920804794520548</v>
       </c>
       <c r="E4">
-        <v>16.55739447850587</v>
+        <v>18.52429386540029</v>
       </c>
       <c r="F4">
         <v>64.91831165609383</v>
       </c>
       <c r="G4">
-        <v>18.52429386540029</v>
+        <v>16.55739447850587</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.99148826412175</v>
+      </c>
+      <c r="C5">
         <v>24.42610265669332</v>
-      </c>
-      <c r="C5">
-        <v>28.99148826412175</v>
       </c>
       <c r="D5">
         <v>4.093980992608237</v>
       </c>
       <c r="E5">
+        <v>18.89710827168796</v>
+      </c>
+      <c r="F5">
+        <v>65.1815736381977</v>
+      </c>
+      <c r="G5">
         <v>15.92131809011432</v>
-      </c>
-      <c r="F5">
-        <v>65.18157363819772</v>
-      </c>
-      <c r="G5">
-        <v>18.89710827168796</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.69052224371373</v>
+      </c>
+      <c r="C6">
         <v>21.08317214700194</v>
-      </c>
-      <c r="C6">
-        <v>29.69052224371373</v>
       </c>
       <c r="D6">
         <v>4.743119266055046</v>
       </c>
       <c r="E6">
-        <v>13.9833226427197</v>
+        <v>19.69211032713278</v>
       </c>
       <c r="F6">
         <v>66.32456703014753</v>
       </c>
       <c r="G6">
-        <v>19.69211032713278</v>
+        <v>13.9833226427197</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.36932241250931</v>
+      </c>
+      <c r="C7">
         <v>27.58749069247952</v>
-      </c>
-      <c r="C7">
-        <v>28.36932241250931</v>
       </c>
       <c r="D7">
         <v>3.624831309041835</v>
       </c>
       <c r="E7">
-        <v>17.68918596323705</v>
+        <v>18.19049892575794</v>
       </c>
       <c r="F7">
         <v>64.12031511100501</v>
       </c>
       <c r="G7">
-        <v>18.19049892575794</v>
+        <v>17.68918596323705</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>22.84122562674095</v>
+      </c>
+      <c r="C8">
         <v>9.470752089136491</v>
-      </c>
-      <c r="C8">
-        <v>22.84122562674095</v>
       </c>
       <c r="D8">
         <v>10.55882352941176</v>
       </c>
       <c r="E8">
-        <v>7.157894736842105</v>
+        <v>17.26315789473684</v>
       </c>
       <c r="F8">
         <v>75.57894736842104</v>
       </c>
       <c r="G8">
-        <v>17.26315789473684</v>
+        <v>7.157894736842105</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.51800554016621</v>
+      </c>
+      <c r="C9">
         <v>18.00554016620499</v>
-      </c>
-      <c r="C9">
-        <v>33.51800554016621</v>
       </c>
       <c r="D9">
         <v>5.553846153846154</v>
       </c>
       <c r="E9">
-        <v>11.88299817184644</v>
+        <v>22.12065813528337</v>
       </c>
       <c r="F9">
         <v>65.99634369287021</v>
       </c>
       <c r="G9">
-        <v>22.12065813528337</v>
+        <v>11.88299817184644</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.56956274843839</v>
+      </c>
+      <c r="C10">
         <v>39.068710959682</v>
-      </c>
-      <c r="C10">
-        <v>27.56956274843839</v>
       </c>
       <c r="D10">
         <v>2.559593023255814</v>
       </c>
       <c r="E10">
-        <v>23.44522065087749</v>
+        <v>16.54455614244334</v>
       </c>
       <c r="F10">
         <v>60.01022320667916</v>
       </c>
       <c r="G10">
-        <v>16.54455614244334</v>
+        <v>23.44522065087749</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.34244455905106</v>
+      </c>
+      <c r="C11">
         <v>39.55647240845797</v>
-      </c>
-      <c r="C11">
-        <v>24.34244455905106</v>
       </c>
       <c r="D11">
         <v>2.528031290743155</v>
       </c>
       <c r="E11">
-        <v>24.13467589679044</v>
+        <v>14.85210824417873</v>
       </c>
       <c r="F11">
         <v>61.01321585903084</v>
       </c>
       <c r="G11">
-        <v>14.85210824417873</v>
+        <v>24.13467589679044</v>
       </c>
     </row>
   </sheetData>
